--- a/output/pdf_financials_xlsx/NTLX.xlsx
+++ b/output/pdf_financials_xlsx/NTLX.xlsx
@@ -468,10 +468,8 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B4" s="3" t="n">
+        <v>1.306</v>
       </c>
     </row>
     <row r="5">
@@ -480,10 +478,8 @@
           <t xml:space="preserve">  Cost of Goods Sold</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B5" s="3" t="n">
+        <v>0.8</v>
       </c>
     </row>
     <row r="6">
@@ -492,10 +488,8 @@
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B6" s="3" t="n">
+        <v>0.506</v>
       </c>
     </row>
     <row r="7">
@@ -504,10 +498,8 @@
           <t xml:space="preserve">  Selling, General, &amp; Admin. Expense</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B7" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -516,10 +508,8 @@
           <t xml:space="preserve">  Research &amp; Development</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -528,10 +518,8 @@
           <t xml:space="preserve">  Other Operating Expense</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B9" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -540,10 +528,8 @@
           <t xml:space="preserve">  Total Operating Expense</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B10" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -552,10 +538,8 @@
           <t>Operating Income</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B11" s="3" t="n">
+        <v>0.506</v>
       </c>
     </row>
     <row r="12">
@@ -564,10 +548,8 @@
           <t xml:space="preserve">    Interest Income</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B12" s="3" t="n">
+        <v>0.022</v>
       </c>
     </row>
     <row r="13">
@@ -576,10 +558,8 @@
           <t xml:space="preserve">    Interest Expense</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B13" s="3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -588,10 +568,8 @@
           <t xml:space="preserve">  Net Interest Income</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B14" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -600,10 +578,8 @@
           <t xml:space="preserve">  Other Income (Expense)</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B15" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -624,10 +600,8 @@
           <t xml:space="preserve">  Tax Provision</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B17" s="3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="18">
@@ -672,10 +646,8 @@
           <t xml:space="preserve">    Net Income (Discontinued Operations)</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B21" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -684,10 +656,8 @@
           <t xml:space="preserve">  Other Income (Minority Interest)</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B22" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -756,10 +726,8 @@
           <t xml:space="preserve">  Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B28" s="3" t="n">
+        <v>0.366</v>
       </c>
     </row>
     <row r="29">
@@ -1488,10 +1456,8 @@
           <t xml:space="preserve">  Cash Flow Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B100" s="3" t="n">
+        <v>0.366</v>
       </c>
     </row>
     <row r="101">
@@ -1500,10 +1466,8 @@
           <t xml:space="preserve">    Change In Receivables</t>
         </is>
       </c>
-      <c r="B101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B101" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -1512,10 +1476,8 @@
           <t xml:space="preserve">    Change In Inventory</t>
         </is>
       </c>
-      <c r="B102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B102" s="3" t="n">
+        <v>0.629</v>
       </c>
     </row>
     <row r="103">
@@ -1524,10 +1486,8 @@
           <t xml:space="preserve">    Change In Prepaid Assets</t>
         </is>
       </c>
-      <c r="B103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B103" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -1536,10 +1496,8 @@
           <t xml:space="preserve">    Change In Payables And Accrued Expense</t>
         </is>
       </c>
-      <c r="B104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B104" s="3" t="n">
+        <v>-0.032</v>
       </c>
     </row>
     <row r="105">
@@ -1548,10 +1506,8 @@
           <t xml:space="preserve">    Change In Other Working Capital</t>
         </is>
       </c>
-      <c r="B105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B105" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -1560,10 +1516,8 @@
           <t xml:space="preserve">  Change In Working Capital</t>
         </is>
       </c>
-      <c r="B106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B106" s="3" t="n">
+        <v>0.597</v>
       </c>
     </row>
     <row r="107">
@@ -1572,10 +1526,8 @@
           <t xml:space="preserve">  Stock Based Compensation</t>
         </is>
       </c>
-      <c r="B107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B107" s="3" t="n">
+        <v>0.045</v>
       </c>
     </row>
     <row r="108">
@@ -1584,10 +1536,8 @@
           <t xml:space="preserve">  Asset Impairment Charge</t>
         </is>
       </c>
-      <c r="B108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B108" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -1596,10 +1546,8 @@
           <t xml:space="preserve">  Cash from Discontinued Operating Activities</t>
         </is>
       </c>
-      <c r="B109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B109" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -1608,10 +1556,8 @@
           <t xml:space="preserve">  Cash Flow from Others</t>
         </is>
       </c>
-      <c r="B110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B110" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -1620,10 +1566,8 @@
           <t xml:space="preserve">  Purchase Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B111" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -1632,10 +1576,8 @@
           <t xml:space="preserve">  Sale Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B112" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -1644,10 +1586,8 @@
           <t xml:space="preserve">  Purchase Of Business</t>
         </is>
       </c>
-      <c r="B113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B113" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -1656,10 +1596,8 @@
           <t xml:space="preserve">  Purchase Of Investment</t>
         </is>
       </c>
-      <c r="B114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B114" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -1668,10 +1606,8 @@
           <t xml:space="preserve">  Sale Of Investment</t>
         </is>
       </c>
-      <c r="B115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B115" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -1680,10 +1616,8 @@
           <t xml:space="preserve">  Net Intangibles Purchase And Sale</t>
         </is>
       </c>
-      <c r="B116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B116" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -1692,10 +1626,8 @@
           <t xml:space="preserve">  Cash From Discontinued Investing Activities</t>
         </is>
       </c>
-      <c r="B117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B117" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -1704,10 +1636,8 @@
           <t xml:space="preserve">  Cash From Other Investing Activities</t>
         </is>
       </c>
-      <c r="B118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B118" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -1716,10 +1646,8 @@
           <t>Cash Flow from Investing</t>
         </is>
       </c>
-      <c r="B119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B119" s="3" t="n">
+        <v>-0.005</v>
       </c>
     </row>
     <row r="120">
@@ -1728,10 +1656,8 @@
           <t xml:space="preserve">  Issuance of Stock</t>
         </is>
       </c>
-      <c r="B120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B120" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -1740,10 +1666,8 @@
           <t xml:space="preserve">  Repurchase of Stock</t>
         </is>
       </c>
-      <c r="B121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B121" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -1752,10 +1676,8 @@
           <t xml:space="preserve">  Net Issuance of Preferred Stock</t>
         </is>
       </c>
-      <c r="B122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B122" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -1764,10 +1686,8 @@
           <t xml:space="preserve">    Issuance of Debt</t>
         </is>
       </c>
-      <c r="B123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B123" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -1776,10 +1696,8 @@
           <t xml:space="preserve">    Payments of Debt</t>
         </is>
       </c>
-      <c r="B124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B124" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -1788,10 +1706,8 @@
           <t xml:space="preserve">  Net Issuance of Debt</t>
         </is>
       </c>
-      <c r="B125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B125" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -1800,10 +1716,8 @@
           <t xml:space="preserve">  Cash Flow for Dividends</t>
         </is>
       </c>
-      <c r="B126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B126" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -1824,10 +1738,8 @@
           <t xml:space="preserve">  Other Financing</t>
         </is>
       </c>
-      <c r="B128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B128" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -1836,10 +1748,8 @@
           <t>Cash Flow from Financing</t>
         </is>
       </c>
-      <c r="B129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B129" s="3" t="n">
+        <v>1.662</v>
       </c>
     </row>
     <row r="130">
@@ -1848,10 +1758,8 @@
           <t xml:space="preserve">  Beginning Cash Position</t>
         </is>
       </c>
-      <c r="B130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B130" s="3" t="n">
+        <v>0.146</v>
       </c>
     </row>
     <row r="131">
@@ -1860,10 +1768,8 @@
           <t xml:space="preserve">    Effect of Exchange Rate Changes</t>
         </is>
       </c>
-      <c r="B131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B131" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -1872,10 +1778,8 @@
           <t xml:space="preserve">  Net Change in Cash</t>
         </is>
       </c>
-      <c r="B132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B132" s="3" t="n">
+        <v>-0.029</v>
       </c>
     </row>
     <row r="133">
@@ -1884,10 +1788,8 @@
           <t>Ending Cash Position</t>
         </is>
       </c>
-      <c r="B133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B133" s="3" t="n">
+        <v>0.117</v>
       </c>
     </row>
     <row r="134">
@@ -1896,10 +1798,8 @@
           <t>Capital Expenditure</t>
         </is>
       </c>
-      <c r="B134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B134" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -1908,10 +1808,8 @@
           <t>Free Cash Flow</t>
         </is>
       </c>
-      <c r="B135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B135" s="3" t="n">
+        <v>-1.686</v>
       </c>
     </row>
   </sheetData>
@@ -1925,7 +1823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2673,6 +2571,828 @@
         <v>1.764</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Cash flows used in operating activities</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Net loss for the period $ (4,363) $</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" s="5" t="n">
+        <v>-4.127</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Cash flows used in operating activities</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Deemed stock exchange listing expense 1,410</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Cash flows used in operating activities</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Amortization and depreciation 194</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>DepreciationAndAmortization</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>0.366</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Cash flows used in operating activities</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Share based compensation 384</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>0.045</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Cash flows used in operating activities</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Finance expenses 51</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Cash flows used in operating activities</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Impairment loss 115</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" s="5" t="n">
+        <v>1.344</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Cash flows used in operating activities</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Change in other accounts receivables (32)</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" s="5" t="n">
+        <v>-0.034</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Cash flows used in operating activities</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Change in trade receivables -</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" s="5" t="n">
+        <v>0.012</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Cash flows used in operating activities</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Change in inventory 38</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>ChangeInInventory</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="n">
+        <v>0.629</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Cash flows used in operating activities</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Change in accounts payable 200</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>-0.032</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Cash flows used in operating activities</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Changes in related parties payables 365</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" s="5" t="n">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Cash flows used in operating activities</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Change in other accounts payable (22)</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" s="5" t="n">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Cash flows used in operating activities</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Cash flows used in operating activities total</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="n">
+        <v>-1.686</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Cash flows from (used in) investing activities</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Restricted deposits -</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" s="5" t="n">
+        <v>-0.005</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Cash flows from (used in) investing activities</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Cash acquired in reverse recapitalization (see note 4) 710</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Cash flows from (used in) investing activities</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Cash flows from (used in) investing activities total</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="n">
+        <v>-0.005</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Cash flows from financing activities</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Loans received (note 14) 1,141</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Cash flows from financing activities</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Parent company contribution 1,393</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" s="5" t="n">
+        <v>1.662</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Cash flows from financing activities</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Cash flows from financing activities total</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="n">
+        <v>1.662</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Cash flows from financing activities</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Increase (decrease) in cash and cash equivalents 1,584</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="n">
+        <v>-0.029</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Cash flows from financing activities</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Cash and cash equivalents at beginning of period 117</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="n">
+        <v>0.146</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Cash flows from financing activities</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Cash and cash equivalents at end of period $ 1,701 $</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="n">
+        <v>0.117</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>details of the accounting treatment.</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>SNI was incorporated in Delaware on August 29,</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" s="5" t="n">
+        <v>2.022</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr"/>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Revenues $ 856 $</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="n">
+        <v>1.306</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Cost of sales                                                                  (225)        (800 )</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Gross profit 631</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>GrossProfit</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="n">
+        <v>0.506</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>General and administrative                                                     (655)         (90 )</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Deemed stock Exchange listing expense (note 4) (1,410)</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Operating loss                                                           $    (4,262) $    (4,149 )</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Finance income 43</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
+      <c r="E58" s="5" t="n">
+        <v>0.022</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Operating loss                                                           $    (4,262) $    (4,149 )</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Finance expenses (125)</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Loss before taxes                                                        $    (4,344) $    (4,127 )</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Tax income (expense) (19)</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Non-controlling interests                                                               (240)      (1,185 )</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Weighted average number of shares outstanding* (note 17) 67,442,466</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="n">
+        <v>63.3</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>BALANCE AT</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>BALANCE AT</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" s="5" t="n">
+        <v>3.958</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Capital</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Capital contribution - 1,707 - 1,707 -</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" s="5" t="n">
+        <v>1.707</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Capital</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Capital contribution 1,456 - 1,456 -</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" s="5" t="n">
+        <v>1.456</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>listing expense</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>(note 4) 18,600,000 1,410 - 1,410</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" s="5" t="n">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>recapitalization</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>(note 4) 17,804 (17,518 ) 286</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" s="5" t="n">
+        <v>0.286</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>compensation</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>(note 4) 3,000,000 321 321</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" s="5" t="n">
+        <v>0.321</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
